--- a/Config/Datas/player_attach.xlsx
+++ b/Config/Datas/player_attach.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="player_attach" sheetId="1" r:id="R30389c742251405f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="player_attach" sheetId="1" r:id="R4a87addebd234b16"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -996,7 +996,7 @@
         <x:v>attach_small</x:v>
       </x:c>
       <x:c r="I5" t="str">
-        <x:v>Prefab/Attach/attach_unit_01</x:v>
+        <x:v>Prefab/Attach/evil_child_attach</x:v>
       </x:c>
       <x:c r="J5" t="n">
         <x:v>-1</x:v>
@@ -1027,7 +1027,9 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" t="str"/>
-      <x:c r="I6" t="str"/>
+      <x:c r="I6" t="str">
+        <x:v>Prefab/Attach/attach_unit_01</x:v>
+      </x:c>
       <x:c r="J6" t="n">
         <x:v>-1</x:v>
       </x:c>
@@ -1039,7 +1041,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb75acca752a4f1f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd786f4a17bbd4b37"/>
   </x:tableParts>
 </x:worksheet>
 </file>